--- a/tooltips.xlsx
+++ b/tooltips.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lpastori\Documents\Avelumab\Visualizador\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leand\Documents\IECS\AVELUMAB\Aplicacion\avelumab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A08FDF40-0C1D-4001-9491-F750160D6F04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0772A5ED-9374-47DF-93E1-D8730203F3BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="103">
   <si>
     <t>Id</t>
   </si>
@@ -65,13 +65,299 @@
   </si>
   <si>
     <t>Incidencia de Cancer de Vejiga en hombres menores de 65 años</t>
+  </si>
+  <si>
+    <t>Costo de 1 vial de Avelumab (200mg)</t>
+  </si>
+  <si>
+    <t>Costo de 1 vial Enfortumab Vedotin (30mg)</t>
+  </si>
+  <si>
+    <t>Costo de 1 vial de Pembrolizumab (200mg)</t>
+  </si>
+  <si>
+    <t>Costo de 1 vial de Nivolumab (240mg)</t>
+  </si>
+  <si>
+    <t>cAvelumab</t>
+  </si>
+  <si>
+    <t>cNivolumab</t>
+  </si>
+  <si>
+    <t>cEV</t>
+  </si>
+  <si>
+    <t>cPembro</t>
+  </si>
+  <si>
+    <t>cCisplatino</t>
+  </si>
+  <si>
+    <t>cCarboplatino</t>
+  </si>
+  <si>
+    <t>cGemcitabine</t>
+  </si>
+  <si>
+    <t>cAtezolizumab</t>
+  </si>
+  <si>
+    <t>cVinflunine</t>
+  </si>
+  <si>
+    <t>cPaclitaxel</t>
+  </si>
+  <si>
+    <t>cErdafitinib</t>
+  </si>
+  <si>
+    <t>cDurvalumab</t>
+  </si>
+  <si>
+    <t>cDocetaxel</t>
+  </si>
+  <si>
+    <t>Costo de 1 vial de Cisplatino (50mg)</t>
+  </si>
+  <si>
+    <t>Costo de 1 vial de Docetaxel (20mg)</t>
+  </si>
+  <si>
+    <t>Costo de 1 vial de Durvalumab (120mg)</t>
+  </si>
+  <si>
+    <t>Costo de 56 comprimidos de Erdafitinib (4mg)</t>
+  </si>
+  <si>
+    <t>Costo de 1 vial de Paclitaxel (300mg)</t>
+  </si>
+  <si>
+    <t>Costo de 1 vial de Vinflunine (250mg)</t>
+  </si>
+  <si>
+    <t>Costo de 1 vial de Atezolizumab (1200mg)</t>
+  </si>
+  <si>
+    <t>Costo de 1 vial de Gemcitabine (1000mg)</t>
+  </si>
+  <si>
+    <t>Costo de 1 vial de Carboplatino (450mg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precio de salida de laboratorio. Alfabeta
+</t>
+  </si>
+  <si>
+    <t>cAdministracion</t>
+  </si>
+  <si>
+    <t>Costo de 1 sesión de quimioterapia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Costo contemplado para un día/turno de infusión en hospital de día.
+</t>
+  </si>
+  <si>
+    <t>cEA_Diarrea</t>
+  </si>
+  <si>
+    <t>cEA_ITU</t>
+  </si>
+  <si>
+    <t>cEA_Anemia</t>
+  </si>
+  <si>
+    <t>cEA_Plqd</t>
+  </si>
+  <si>
+    <t>cEA_GBd</t>
+  </si>
+  <si>
+    <t>cEA_Hiperglu</t>
+  </si>
+  <si>
+    <t>cEA_Rash</t>
+  </si>
+  <si>
+    <t>cEA_Neutd</t>
+  </si>
+  <si>
+    <t>cEA_Pnp</t>
+  </si>
+  <si>
+    <t>pSD_AVE</t>
+  </si>
+  <si>
+    <t>pSD_BSC</t>
+  </si>
+  <si>
+    <t>pSD_QMTNR</t>
+  </si>
+  <si>
+    <t>pSD_NIV</t>
+  </si>
+  <si>
+    <t>pSD_EVP</t>
+  </si>
+  <si>
+    <t>msEVPEB1</t>
+  </si>
+  <si>
+    <t>msEVPEB2</t>
+  </si>
+  <si>
+    <t>msEVPEB3</t>
+  </si>
+  <si>
+    <t>msEVPEB4</t>
+  </si>
+  <si>
+    <t>msEVPEB5</t>
+  </si>
+  <si>
+    <t>msNIVEB1</t>
+  </si>
+  <si>
+    <t>msNIVEB2</t>
+  </si>
+  <si>
+    <t>msNIVEB3</t>
+  </si>
+  <si>
+    <t>msNIVEB4</t>
+  </si>
+  <si>
+    <t>msNIVEB5</t>
+  </si>
+  <si>
+    <t>msAVEEB1</t>
+  </si>
+  <si>
+    <t>msAVEEB2</t>
+  </si>
+  <si>
+    <t>msAVEEB3</t>
+  </si>
+  <si>
+    <t>msAVEEB4</t>
+  </si>
+  <si>
+    <t>msAVEEB5</t>
+  </si>
+  <si>
+    <t>msEVPEP1</t>
+  </si>
+  <si>
+    <t>msEVPEP2</t>
+  </si>
+  <si>
+    <t>msEVPEP3</t>
+  </si>
+  <si>
+    <t>msEVPEP4</t>
+  </si>
+  <si>
+    <t>msEVPEP5</t>
+  </si>
+  <si>
+    <t>msNIVEP1</t>
+  </si>
+  <si>
+    <t>msNIVEP2</t>
+  </si>
+  <si>
+    <t>msNIVEP3</t>
+  </si>
+  <si>
+    <t>msNIVEP4</t>
+  </si>
+  <si>
+    <t>msNIVEP5</t>
+  </si>
+  <si>
+    <t>msAVEEP1</t>
+  </si>
+  <si>
+    <t>msAVEEP2</t>
+  </si>
+  <si>
+    <t>msAVEEP3</t>
+  </si>
+  <si>
+    <t>msAVEEP4</t>
+  </si>
+  <si>
+    <t>msAVEEP5</t>
+  </si>
+  <si>
+    <t>Diarrea</t>
+  </si>
+  <si>
+    <t>Infección Urinaria</t>
+  </si>
+  <si>
+    <t>Anemia</t>
+  </si>
+  <si>
+    <t>Plaquetopenia</t>
+  </si>
+  <si>
+    <t>Leucopenia</t>
+  </si>
+  <si>
+    <t>Hiperglucemia</t>
+  </si>
+  <si>
+    <t>Rash</t>
+  </si>
+  <si>
+    <t>Neutropenia</t>
+  </si>
+  <si>
+    <t>Polineuropatia Periferica</t>
+  </si>
+  <si>
+    <t>Probabilidad de tratamiento subsecuente tras QMT + Avelumab</t>
+  </si>
+  <si>
+    <t>Probabilidad de tratamiento subsecuente tras QMT + BSC</t>
+  </si>
+  <si>
+    <t>Probabilidad de tratamiento subsecuente tras QMT</t>
+  </si>
+  <si>
+    <t>Probabilidad de tratamiento subsecuente tras QMT + Nivolumab</t>
+  </si>
+  <si>
+    <t>Probabilidad de tratamiento subsecuente tras EV + Pembrolizumab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probabilidad de recibir tratamientos subsecuentes dado que el paciente recibió quimioterapia seguida de Avelumab
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probabilidad de recibir tratamientos subsecuentes dado que el paciente recibió quimioterapia seguida de BSC
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probabilidad de recibir tratamientos subsecuentes dado que el paciente recibió quimioterapia y no respondio
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probabilidad de recibir tratamientos subsecuentes dado que el paciente recibió quimioterapia asociada a Nivolumab
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probabilidad de recibir tratamientos subsecuentes dado que el paciente recibió Enfortumab Vedotin + Pembrolizumab
+</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -117,8 +403,14 @@
       <color theme="1"/>
       <name val="&quot;Aptos Narrow&quot;"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -131,14 +423,8 @@
         <bgColor rgb="FF8EAADB"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -158,6 +444,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -181,8 +482,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -399,16 +704,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y982"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="27.6640625" customWidth="1"/>
-    <col min="2" max="2" width="73.33203125" customWidth="1"/>
-    <col min="3" max="3" width="92.5546875" customWidth="1"/>
-    <col min="4" max="4" width="20.88671875" customWidth="1"/>
-    <col min="5" max="25" width="9.109375" customWidth="1"/>
+    <col min="1" max="1" width="27.7109375" customWidth="1"/>
+    <col min="2" max="2" width="73.28515625" customWidth="1"/>
+    <col min="3" max="3" width="92.5703125" customWidth="1"/>
+    <col min="4" max="4" width="20.85546875" customWidth="1"/>
+    <col min="5" max="25" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="14.4">
+    <row r="1" spans="1:25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -422,7 +727,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="25.2" customHeight="1">
+    <row r="2" spans="1:25" ht="25.15" customHeight="1">
       <c r="A2" s="6" t="s">
         <v>6</v>
       </c>
@@ -436,7 +741,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="25.2" customHeight="1">
+    <row r="3" spans="1:25" ht="25.15" customHeight="1">
       <c r="A3" s="6" t="s">
         <v>7</v>
       </c>
@@ -450,23 +755,47 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="25.2" customHeight="1">
-      <c r="A4" s="7"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="2"/>
-    </row>
-    <row r="5" spans="1:25" ht="25.2" customHeight="1">
-      <c r="A5" s="7"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="2"/>
-    </row>
-    <row r="6" spans="1:25" ht="25.2" customHeight="1">
-      <c r="A6" s="8"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="2"/>
+    <row r="4" spans="1:25" ht="25.15" customHeight="1">
+      <c r="A4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" ht="25.15" customHeight="1">
+      <c r="A5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" ht="25.15" customHeight="1">
+      <c r="A6" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>4</v>
+      </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
@@ -489,11 +818,19 @@
       <c r="X6" s="3"/>
       <c r="Y6" s="3"/>
     </row>
-    <row r="7" spans="1:25" ht="25.2" customHeight="1">
-      <c r="A7" s="8"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="2"/>
+    <row r="7" spans="1:25" ht="25.15" customHeight="1">
+      <c r="A7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>4</v>
+      </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
@@ -516,41 +853,89 @@
       <c r="X7" s="3"/>
       <c r="Y7" s="3"/>
     </row>
-    <row r="8" spans="1:25" ht="25.2" customHeight="1">
-      <c r="A8" s="8"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="2"/>
-    </row>
-    <row r="9" spans="1:25" ht="25.2" customHeight="1">
-      <c r="A9" s="8"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="2"/>
-    </row>
-    <row r="10" spans="1:25" ht="25.2" customHeight="1">
-      <c r="A10" s="8"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="11" spans="1:25" ht="25.2" customHeight="1">
-      <c r="A11" s="8"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="2"/>
-    </row>
-    <row r="12" spans="1:25" ht="25.2" customHeight="1">
-      <c r="A12" s="8"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="2"/>
-    </row>
-    <row r="13" spans="1:25" ht="25.2" customHeight="1">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="2"/>
+    <row r="8" spans="1:25" ht="25.15" customHeight="1">
+      <c r="A8" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" ht="25.15" customHeight="1">
+      <c r="A9" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" ht="25.15" customHeight="1">
+      <c r="A10" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" ht="25.15" customHeight="1">
+      <c r="A11" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" ht="25.15" customHeight="1">
+      <c r="A12" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" ht="25.15" customHeight="1">
+      <c r="A13" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>4</v>
+      </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
@@ -573,188 +958,622 @@
       <c r="X13" s="3"/>
       <c r="Y13" s="3"/>
     </row>
-    <row r="14" spans="1:25" ht="25.2" customHeight="1">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="2"/>
-    </row>
-    <row r="15" spans="1:25" ht="25.2" customHeight="1">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="2"/>
-    </row>
-    <row r="16" spans="1:25" ht="25.2" customHeight="1">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="2"/>
-    </row>
-    <row r="17" spans="1:8" ht="25.2" customHeight="1">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="2"/>
-    </row>
-    <row r="18" spans="1:8" ht="25.2" customHeight="1">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="2"/>
-    </row>
-    <row r="19" spans="1:8" ht="25.2" customHeight="1">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="2"/>
-    </row>
-    <row r="20" spans="1:8" ht="25.2" customHeight="1">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="2"/>
-    </row>
-    <row r="21" spans="1:8" ht="25.2" customHeight="1">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="2"/>
-    </row>
-    <row r="22" spans="1:8" ht="25.2" customHeight="1">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="2"/>
-    </row>
-    <row r="23" spans="1:8" ht="25.2" customHeight="1">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="2"/>
-    </row>
-    <row r="24" spans="1:8" ht="25.2" customHeight="1">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="2"/>
-    </row>
-    <row r="25" spans="1:8" ht="25.2" customHeight="1">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="2"/>
+    <row r="14" spans="1:25" ht="25.15" customHeight="1">
+      <c r="A14" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" ht="25.15" customHeight="1">
+      <c r="A15" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" ht="25.15" customHeight="1">
+      <c r="A16" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="25.15" customHeight="1">
+      <c r="A17" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="25.15" customHeight="1">
+      <c r="A18" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="25.15" customHeight="1">
+      <c r="A19" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="25.15" customHeight="1">
+      <c r="A20" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="25.15" customHeight="1">
+      <c r="A21" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="25.15" customHeight="1">
+      <c r="A22" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="25.15" customHeight="1">
+      <c r="A23" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="25.15" customHeight="1">
+      <c r="A24" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="25.15" customHeight="1">
+      <c r="A25" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="26" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="2"/>
+      <c r="A26" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="27" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="2"/>
+      <c r="A27" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="28" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="2"/>
+      <c r="A28" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="29" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="2"/>
+      <c r="A29" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="30" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="2"/>
+      <c r="A30" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="31" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="2"/>
+      <c r="A31" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>4</v>
+      </c>
       <c r="H31" s="5"/>
     </row>
     <row r="32" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A32" s="9"/>
+      <c r="A32" s="9" t="s">
+        <v>54</v>
+      </c>
       <c r="B32" s="9"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="2"/>
+      <c r="C32" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="33" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A33" s="9"/>
+      <c r="A33" s="10" t="s">
+        <v>55</v>
+      </c>
       <c r="B33" s="9"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="2"/>
+      <c r="C33" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="34" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A34" s="9"/>
+      <c r="A34" s="10" t="s">
+        <v>56</v>
+      </c>
       <c r="B34" s="9"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="2"/>
+      <c r="C34" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="35" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A35" s="9"/>
+      <c r="A35" s="10" t="s">
+        <v>57</v>
+      </c>
       <c r="B35" s="9"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="2"/>
+      <c r="C35" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="36" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A36" s="9"/>
+      <c r="A36" s="10" t="s">
+        <v>58</v>
+      </c>
       <c r="B36" s="9"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="2"/>
+      <c r="C36" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="37" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A37" s="9"/>
+      <c r="A37" s="10" t="s">
+        <v>59</v>
+      </c>
       <c r="B37" s="9"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="2"/>
+      <c r="C37" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="38" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A38" s="9"/>
+      <c r="A38" s="10" t="s">
+        <v>60</v>
+      </c>
       <c r="B38" s="9"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="2"/>
+      <c r="C38" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="39" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A39" s="10"/>
-      <c r="B39" s="10"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="2"/>
-    </row>
-    <row r="40" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="41" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="42" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="43" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="44" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="45" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="46" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="47" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="48" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="49" ht="15.75" customHeight="1"/>
-    <row r="50" ht="15.75" customHeight="1"/>
-    <row r="51" ht="15.75" customHeight="1"/>
-    <row r="52" ht="15.75" customHeight="1"/>
-    <row r="53" ht="15.75" customHeight="1"/>
-    <row r="54" ht="15.75" customHeight="1"/>
-    <row r="55" ht="15.75" customHeight="1"/>
-    <row r="56" ht="15.75" customHeight="1"/>
-    <row r="57" ht="15.75" customHeight="1"/>
-    <row r="58" ht="15.75" customHeight="1"/>
-    <row r="59" ht="15.75" customHeight="1"/>
-    <row r="60" ht="15.75" customHeight="1"/>
-    <row r="61" ht="15.75" customHeight="1"/>
-    <row r="62" ht="15.75" customHeight="1"/>
-    <row r="63" ht="15.75" customHeight="1"/>
-    <row r="64" ht="15.75" customHeight="1"/>
+      <c r="A39" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B39" s="9"/>
+      <c r="C39" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A40" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B40" s="9"/>
+      <c r="C40" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A41" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="B41" s="9"/>
+      <c r="C41" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A42" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B42" s="9"/>
+      <c r="C42" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A43" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B43" s="9"/>
+      <c r="C43" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A44" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B44" s="9"/>
+      <c r="C44" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A45" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="B45" s="9"/>
+      <c r="C45" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A46" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="B46" s="9"/>
+      <c r="C46" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A47" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B47" s="9"/>
+      <c r="C47" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A48" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B48" s="9"/>
+      <c r="C48" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A49" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="B49" s="9"/>
+      <c r="C49" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A50" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="B50" s="9"/>
+      <c r="C50" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A51" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="B51" s="9"/>
+      <c r="C51" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A52" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="B52" s="9"/>
+      <c r="C52" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A53" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B53" s="9"/>
+      <c r="C53" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A54" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B54" s="9"/>
+      <c r="C54" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A55" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B55" s="9"/>
+      <c r="C55" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A56" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B56" s="9"/>
+      <c r="C56" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A57" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="B57" s="9"/>
+      <c r="C57" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A58" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B58" s="9"/>
+      <c r="C58" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A59" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B59" s="9"/>
+      <c r="C59" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A60" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="B60" s="9"/>
+      <c r="C60" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A61" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B61" s="9"/>
+      <c r="C61" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="63" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="64" spans="1:4" ht="15.75" customHeight="1"/>
     <row r="65" ht="15.75" customHeight="1"/>
     <row r="66" ht="15.75" customHeight="1"/>
     <row r="67" ht="15.75" customHeight="1"/>

--- a/tooltips.xlsx
+++ b/tooltips.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leand\Documents\IECS\AVELUMAB\Aplicacion\avelumab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0772A5ED-9374-47DF-93E1-D8730203F3BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01E8C375-878C-4A34-9DBA-4C91825149F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="107">
   <si>
     <t>Id</t>
   </si>
@@ -351,6 +351,18 @@
   <si>
     <t xml:space="preserve">Probabilidad de recibir tratamientos subsecuentes dado que el paciente recibió Enfortumab Vedotin + Pembrolizumab
 </t>
+  </si>
+  <si>
+    <t>tHT</t>
+  </si>
+  <si>
+    <t>Horizonte Temporal</t>
+  </si>
+  <si>
+    <t>pAnualGrowth</t>
+  </si>
+  <si>
+    <t>Crecimiento Poblacional</t>
   </si>
 </sst>
 </file>
@@ -1571,8 +1583,34 @@
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="63" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="62" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A62" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A63" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
     <row r="64" spans="1:4" ht="15.75" customHeight="1"/>
     <row r="65" ht="15.75" customHeight="1"/>
     <row r="66" ht="15.75" customHeight="1"/>

--- a/tooltips.xlsx
+++ b/tooltips.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">

--- a/tooltips.xlsx
+++ b/tooltips.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leand\Documents\IECS\AVELUMAB\Aplicacion\avelumab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01E8C375-878C-4A34-9DBA-4C91825149F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29C123CB-D1DC-402F-8A95-E6FCA38C0D20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="108">
   <si>
     <t>Id</t>
   </si>
@@ -51,20 +51,10 @@
     <t>top</t>
   </si>
   <si>
-    <t xml:space="preserve">Descripción y referencia del parámetro
-</t>
-  </si>
-  <si>
-    <t>nIncidenciaH064</t>
-  </si>
-  <si>
     <t>nAfiliados</t>
   </si>
   <si>
     <t>Número de Afiliados</t>
-  </si>
-  <si>
-    <t>Incidencia de Cancer de Vejiga en hombres menores de 65 años</t>
   </si>
   <si>
     <t>Costo de 1 vial de Avelumab (200mg)</t>
@@ -155,214 +145,228 @@
     <t>Costo de 1 sesión de quimioterapia</t>
   </si>
   <si>
-    <t xml:space="preserve">Costo contemplado para un día/turno de infusión en hospital de día.
+    <t>cEA_Diarrea</t>
+  </si>
+  <si>
+    <t>cEA_ITU</t>
+  </si>
+  <si>
+    <t>cEA_Anemia</t>
+  </si>
+  <si>
+    <t>cEA_Plqd</t>
+  </si>
+  <si>
+    <t>cEA_GBd</t>
+  </si>
+  <si>
+    <t>cEA_Hiperglu</t>
+  </si>
+  <si>
+    <t>cEA_Rash</t>
+  </si>
+  <si>
+    <t>cEA_Neutd</t>
+  </si>
+  <si>
+    <t>cEA_Pnp</t>
+  </si>
+  <si>
+    <t>pSD_AVE</t>
+  </si>
+  <si>
+    <t>pSD_BSC</t>
+  </si>
+  <si>
+    <t>pSD_QMTNR</t>
+  </si>
+  <si>
+    <t>pSD_NIV</t>
+  </si>
+  <si>
+    <t>pSD_EVP</t>
+  </si>
+  <si>
+    <t>msEVPEB1</t>
+  </si>
+  <si>
+    <t>msEVPEB2</t>
+  </si>
+  <si>
+    <t>msEVPEB3</t>
+  </si>
+  <si>
+    <t>msEVPEB4</t>
+  </si>
+  <si>
+    <t>msEVPEB5</t>
+  </si>
+  <si>
+    <t>msNIVEB1</t>
+  </si>
+  <si>
+    <t>msNIVEB2</t>
+  </si>
+  <si>
+    <t>msNIVEB3</t>
+  </si>
+  <si>
+    <t>msNIVEB4</t>
+  </si>
+  <si>
+    <t>msNIVEB5</t>
+  </si>
+  <si>
+    <t>msAVEEB1</t>
+  </si>
+  <si>
+    <t>msAVEEB2</t>
+  </si>
+  <si>
+    <t>msAVEEB3</t>
+  </si>
+  <si>
+    <t>msAVEEB4</t>
+  </si>
+  <si>
+    <t>msAVEEB5</t>
+  </si>
+  <si>
+    <t>msEVPEP1</t>
+  </si>
+  <si>
+    <t>msEVPEP2</t>
+  </si>
+  <si>
+    <t>msEVPEP3</t>
+  </si>
+  <si>
+    <t>msEVPEP4</t>
+  </si>
+  <si>
+    <t>msEVPEP5</t>
+  </si>
+  <si>
+    <t>msNIVEP1</t>
+  </si>
+  <si>
+    <t>msNIVEP2</t>
+  </si>
+  <si>
+    <t>msNIVEP3</t>
+  </si>
+  <si>
+    <t>msNIVEP4</t>
+  </si>
+  <si>
+    <t>msNIVEP5</t>
+  </si>
+  <si>
+    <t>msAVEEP1</t>
+  </si>
+  <si>
+    <t>msAVEEP2</t>
+  </si>
+  <si>
+    <t>msAVEEP3</t>
+  </si>
+  <si>
+    <t>msAVEEP4</t>
+  </si>
+  <si>
+    <t>msAVEEP5</t>
+  </si>
+  <si>
+    <t>Diarrea</t>
+  </si>
+  <si>
+    <t>Infección Urinaria</t>
+  </si>
+  <si>
+    <t>Anemia</t>
+  </si>
+  <si>
+    <t>Plaquetopenia</t>
+  </si>
+  <si>
+    <t>Leucopenia</t>
+  </si>
+  <si>
+    <t>Hiperglucemia</t>
+  </si>
+  <si>
+    <t>Rash</t>
+  </si>
+  <si>
+    <t>Neutropenia</t>
+  </si>
+  <si>
+    <t>Polineuropatia Periferica</t>
+  </si>
+  <si>
+    <t>Probabilidad de tratamiento subsecuente tras QMT + Avelumab</t>
+  </si>
+  <si>
+    <t>Probabilidad de tratamiento subsecuente tras QMT + BSC</t>
+  </si>
+  <si>
+    <t>Probabilidad de tratamiento subsecuente tras QMT</t>
+  </si>
+  <si>
+    <t>Probabilidad de tratamiento subsecuente tras QMT + Nivolumab</t>
+  </si>
+  <si>
+    <t>Probabilidad de tratamiento subsecuente tras EV + Pembrolizumab</t>
+  </si>
+  <si>
+    <t>tHT</t>
+  </si>
+  <si>
+    <t>Horizonte Temporal</t>
+  </si>
+  <si>
+    <t>pAnualGrowth</t>
+  </si>
+  <si>
+    <t>Crecimiento Poblacional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Número de personas cubiertas.
 </t>
   </si>
   <si>
-    <t>cEA_Diarrea</t>
-  </si>
-  <si>
-    <t>cEA_ITU</t>
-  </si>
-  <si>
-    <t>cEA_Anemia</t>
-  </si>
-  <si>
-    <t>cEA_Plqd</t>
-  </si>
-  <si>
-    <t>cEA_GBd</t>
-  </si>
-  <si>
-    <t>cEA_Hiperglu</t>
-  </si>
-  <si>
-    <t>cEA_Rash</t>
-  </si>
-  <si>
-    <t>cEA_Neutd</t>
-  </si>
-  <si>
-    <t>cEA_Pnp</t>
-  </si>
-  <si>
-    <t>pSD_AVE</t>
-  </si>
-  <si>
-    <t>pSD_BSC</t>
-  </si>
-  <si>
-    <t>pSD_QMTNR</t>
-  </si>
-  <si>
-    <t>pSD_NIV</t>
-  </si>
-  <si>
-    <t>pSD_EVP</t>
-  </si>
-  <si>
-    <t>msEVPEB1</t>
-  </si>
-  <si>
-    <t>msEVPEB2</t>
-  </si>
-  <si>
-    <t>msEVPEB3</t>
-  </si>
-  <si>
-    <t>msEVPEB4</t>
-  </si>
-  <si>
-    <t>msEVPEB5</t>
-  </si>
-  <si>
-    <t>msNIVEB1</t>
-  </si>
-  <si>
-    <t>msNIVEB2</t>
-  </si>
-  <si>
-    <t>msNIVEB3</t>
-  </si>
-  <si>
-    <t>msNIVEB4</t>
-  </si>
-  <si>
-    <t>msNIVEB5</t>
-  </si>
-  <si>
-    <t>msAVEEB1</t>
-  </si>
-  <si>
-    <t>msAVEEB2</t>
-  </si>
-  <si>
-    <t>msAVEEB3</t>
-  </si>
-  <si>
-    <t>msAVEEB4</t>
-  </si>
-  <si>
-    <t>msAVEEB5</t>
-  </si>
-  <si>
-    <t>msEVPEP1</t>
-  </si>
-  <si>
-    <t>msEVPEP2</t>
-  </si>
-  <si>
-    <t>msEVPEP3</t>
-  </si>
-  <si>
-    <t>msEVPEP4</t>
-  </si>
-  <si>
-    <t>msEVPEP5</t>
-  </si>
-  <si>
-    <t>msNIVEP1</t>
-  </si>
-  <si>
-    <t>msNIVEP2</t>
-  </si>
-  <si>
-    <t>msNIVEP3</t>
-  </si>
-  <si>
-    <t>msNIVEP4</t>
-  </si>
-  <si>
-    <t>msNIVEP5</t>
-  </si>
-  <si>
-    <t>msAVEEP1</t>
-  </si>
-  <si>
-    <t>msAVEEP2</t>
-  </si>
-  <si>
-    <t>msAVEEP3</t>
-  </si>
-  <si>
-    <t>msAVEEP4</t>
-  </si>
-  <si>
-    <t>msAVEEP5</t>
-  </si>
-  <si>
-    <t>Diarrea</t>
-  </si>
-  <si>
-    <t>Infección Urinaria</t>
-  </si>
-  <si>
-    <t>Anemia</t>
-  </si>
-  <si>
-    <t>Plaquetopenia</t>
-  </si>
-  <si>
-    <t>Leucopenia</t>
-  </si>
-  <si>
-    <t>Hiperglucemia</t>
-  </si>
-  <si>
-    <t>Rash</t>
-  </si>
-  <si>
-    <t>Neutropenia</t>
-  </si>
-  <si>
-    <t>Polineuropatia Periferica</t>
-  </si>
-  <si>
-    <t>Probabilidad de tratamiento subsecuente tras QMT + Avelumab</t>
-  </si>
-  <si>
-    <t>Probabilidad de tratamiento subsecuente tras QMT + BSC</t>
-  </si>
-  <si>
-    <t>Probabilidad de tratamiento subsecuente tras QMT</t>
-  </si>
-  <si>
-    <t>Probabilidad de tratamiento subsecuente tras QMT + Nivolumab</t>
-  </si>
-  <si>
-    <t>Probabilidad de tratamiento subsecuente tras EV + Pembrolizumab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Probabilidad de recibir tratamientos subsecuentes dado que el paciente recibió quimioterapia seguida de Avelumab
+    <t>Costo contemplado para un día/turno de infusión en hospital de día. BCU IECS.</t>
+  </si>
+  <si>
+    <t>Costo de presentar el evento adverso, microcosteo. BCU IECS.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probabilidad de recibir tratamientos subsecuentes dado que el paciente recibió quimioterapia seguida de Avelumab. Opinion de Experto.
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Probabilidad de recibir tratamientos subsecuentes dado que el paciente recibió quimioterapia seguida de BSC
+    <t xml:space="preserve">Probabilidad de recibir tratamientos subsecuentes dado que el paciente recibió quimioterapia seguida de BSC. Opinion de Experto.
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Probabilidad de recibir tratamientos subsecuentes dado que el paciente recibió quimioterapia y no respondio
+    <t xml:space="preserve">Probabilidad de recibir tratamientos subsecuentes dado que el paciente recibió quimioterapia y no respondio. Opinion de Experto.
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Probabilidad de recibir tratamientos subsecuentes dado que el paciente recibió quimioterapia asociada a Nivolumab
+    <t xml:space="preserve">Probabilidad de recibir tratamientos subsecuentes dado que el paciente recibió quimioterapia asociada a Nivolumab. Opinion de Experto.
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Probabilidad de recibir tratamientos subsecuentes dado que el paciente recibió Enfortumab Vedotin + Pembrolizumab
+    <t xml:space="preserve">Probabilidad de recibir tratamientos subsecuentes dado que el paciente recibió Enfortumab Vedotin + Pembrolizumab. Opinion de Experto.
 </t>
   </si>
   <si>
-    <t>tHT</t>
-  </si>
-  <si>
-    <t>Horizonte Temporal</t>
-  </si>
-  <si>
-    <t>pAnualGrowth</t>
-  </si>
-  <si>
-    <t>Crecimiento Poblacional</t>
+    <t xml:space="preserve">Cantidad de años que contempla el análisis
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% de crecimiento de los afiliados
+</t>
   </si>
 </sst>
 </file>
@@ -715,7 +719,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y982"/>
+  <sheetPr codeName="Hoja1"/>
+  <dimension ref="A1:Y981"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="27.7109375" customWidth="1"/>
@@ -741,27 +746,27 @@
     </row>
     <row r="2" spans="1:25" ht="25.15" customHeight="1">
       <c r="A2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>9</v>
-      </c>
       <c r="C2" s="4" t="s">
-        <v>5</v>
+        <v>98</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:25" ht="25.15" customHeight="1">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>8</v>
-      </c>
       <c r="C3" s="4" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>4</v>
@@ -769,41 +774,62 @@
     </row>
     <row r="4" spans="1:25" ht="25.15" customHeight="1">
       <c r="A4" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" ht="25.15" customHeight="1">
+      <c r="A5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" ht="25.15" customHeight="1">
-      <c r="A5" s="7" t="s">
-        <v>16</v>
-      </c>
       <c r="B5" s="9" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
+      <c r="S5" s="3"/>
+      <c r="T5" s="3"/>
+      <c r="U5" s="3"/>
+      <c r="V5" s="3"/>
+      <c r="W5" s="3"/>
+      <c r="X5" s="3"/>
+      <c r="Y5" s="3"/>
     </row>
     <row r="6" spans="1:25" ht="25.15" customHeight="1">
       <c r="A6" s="8" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>4</v>
@@ -831,49 +857,28 @@
       <c r="Y6" s="3"/>
     </row>
     <row r="7" spans="1:25" ht="25.15" customHeight="1">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="9" t="s">
         <v>15</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-      <c r="S7" s="3"/>
-      <c r="T7" s="3"/>
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
-      <c r="W7" s="3"/>
-      <c r="X7" s="3"/>
-      <c r="Y7" s="3"/>
     </row>
     <row r="8" spans="1:25" ht="25.15" customHeight="1">
       <c r="A8" s="9" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>4</v>
@@ -881,13 +886,13 @@
     </row>
     <row r="9" spans="1:25" ht="25.15" customHeight="1">
       <c r="A9" s="9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>4</v>
@@ -895,13 +900,13 @@
     </row>
     <row r="10" spans="1:25" ht="25.15" customHeight="1">
       <c r="A10" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>4</v>
@@ -909,13 +914,13 @@
     </row>
     <row r="11" spans="1:25" ht="25.15" customHeight="1">
       <c r="A11" s="9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B11" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>33</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>36</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>4</v>
@@ -923,62 +928,62 @@
     </row>
     <row r="12" spans="1:25" ht="25.15" customHeight="1">
       <c r="A12" s="9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="3"/>
+      <c r="S12" s="3"/>
+      <c r="T12" s="3"/>
+      <c r="U12" s="3"/>
+      <c r="V12" s="3"/>
+      <c r="W12" s="3"/>
+      <c r="X12" s="3"/>
+      <c r="Y12" s="3"/>
     </row>
     <row r="13" spans="1:25" ht="25.15" customHeight="1">
       <c r="A13" s="9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
-      <c r="S13" s="3"/>
-      <c r="T13" s="3"/>
-      <c r="U13" s="3"/>
-      <c r="V13" s="3"/>
-      <c r="W13" s="3"/>
-      <c r="X13" s="3"/>
-      <c r="Y13" s="3"/>
     </row>
     <row r="14" spans="1:25" ht="25.15" customHeight="1">
       <c r="A14" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>4</v>
@@ -986,13 +991,13 @@
     </row>
     <row r="15" spans="1:25" ht="25.15" customHeight="1">
       <c r="A15" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="9" t="s">
-        <v>29</v>
-      </c>
       <c r="C15" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>4</v>
@@ -1000,13 +1005,13 @@
     </row>
     <row r="16" spans="1:25" ht="25.15" customHeight="1">
       <c r="A16" s="9" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>36</v>
+        <v>99</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>4</v>
@@ -1014,13 +1019,13 @@
     </row>
     <row r="17" spans="1:8" ht="25.15" customHeight="1">
       <c r="A17" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>39</v>
+        <v>100</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>4</v>
@@ -1028,13 +1033,13 @@
     </row>
     <row r="18" spans="1:8" ht="25.15" customHeight="1">
       <c r="A18" s="9" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>4</v>
@@ -1042,13 +1047,13 @@
     </row>
     <row r="19" spans="1:8" ht="25.15" customHeight="1">
       <c r="A19" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>4</v>
@@ -1056,13 +1061,13 @@
     </row>
     <row r="20" spans="1:8" ht="25.15" customHeight="1">
       <c r="A20" s="9" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>4</v>
@@ -1070,13 +1075,13 @@
     </row>
     <row r="21" spans="1:8" ht="25.15" customHeight="1">
       <c r="A21" s="9" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>4</v>
@@ -1084,13 +1089,13 @@
     </row>
     <row r="22" spans="1:8" ht="25.15" customHeight="1">
       <c r="A22" s="9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>4</v>
@@ -1098,13 +1103,13 @@
     </row>
     <row r="23" spans="1:8" ht="25.15" customHeight="1">
       <c r="A23" s="9" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>4</v>
@@ -1112,27 +1117,27 @@
     </row>
     <row r="24" spans="1:8" ht="25.15" customHeight="1">
       <c r="A24" s="9" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="25.15" customHeight="1">
+    <row r="25" spans="1:8" ht="15.75" customHeight="1">
       <c r="A25" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>4</v>
@@ -1140,13 +1145,13 @@
     </row>
     <row r="26" spans="1:8" ht="15.75" customHeight="1">
       <c r="A26" s="9" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>36</v>
+        <v>101</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>4</v>
@@ -1154,41 +1159,41 @@
     </row>
     <row r="27" spans="1:8" ht="15.75" customHeight="1">
       <c r="A27" s="9" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A28" s="9" t="s">
-        <v>50</v>
+      <c r="A28" s="10" t="s">
+        <v>47</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A29" s="10" t="s">
-        <v>51</v>
+      <c r="A29" s="9" t="s">
+        <v>48</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>4</v>
@@ -1196,388 +1201,328 @@
     </row>
     <row r="30" spans="1:8" ht="15.75" customHeight="1">
       <c r="A30" s="9" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="H30" s="5"/>
     </row>
     <row r="31" spans="1:8" ht="15.75" customHeight="1">
       <c r="A31" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>102</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="B31" s="9"/>
+      <c r="C31" s="4"/>
       <c r="D31" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H31" s="5"/>
     </row>
     <row r="32" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A32" s="9" t="s">
-        <v>54</v>
+      <c r="A32" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="B32" s="9"/>
-      <c r="C32" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="C32" s="4"/>
       <c r="D32" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="15.75" customHeight="1">
       <c r="A33" s="10" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B33" s="9"/>
-      <c r="C33" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="C33" s="4"/>
       <c r="D33" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="15.75" customHeight="1">
       <c r="A34" s="10" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B34" s="9"/>
-      <c r="C34" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="C34" s="4"/>
       <c r="D34" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="15.75" customHeight="1">
       <c r="A35" s="10" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B35" s="9"/>
-      <c r="C35" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="C35" s="4"/>
       <c r="D35" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="15.75" customHeight="1">
       <c r="A36" s="10" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B36" s="9"/>
-      <c r="C36" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="C36" s="4"/>
       <c r="D36" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="15.75" customHeight="1">
       <c r="A37" s="10" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B37" s="9"/>
-      <c r="C37" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="C37" s="4"/>
       <c r="D37" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="15.75" customHeight="1">
       <c r="A38" s="10" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B38" s="9"/>
-      <c r="C38" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="C38" s="4"/>
       <c r="D38" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="15.75" customHeight="1">
       <c r="A39" s="10" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B39" s="9"/>
-      <c r="C39" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="C39" s="4"/>
       <c r="D39" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="15.75" customHeight="1">
       <c r="A40" s="10" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B40" s="9"/>
-      <c r="C40" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="C40" s="4"/>
       <c r="D40" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A41" s="10" t="s">
-        <v>63</v>
+      <c r="A41" s="9" t="s">
+        <v>60</v>
       </c>
       <c r="B41" s="9"/>
-      <c r="C41" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="C41" s="4"/>
       <c r="D41" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A42" s="9" t="s">
-        <v>64</v>
+      <c r="A42" s="10" t="s">
+        <v>61</v>
       </c>
       <c r="B42" s="9"/>
-      <c r="C42" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="C42" s="4"/>
       <c r="D42" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="15.75" customHeight="1">
       <c r="A43" s="10" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B43" s="9"/>
-      <c r="C43" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="C43" s="4"/>
       <c r="D43" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="15.75" customHeight="1">
       <c r="A44" s="10" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B44" s="9"/>
-      <c r="C44" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="C44" s="4"/>
       <c r="D44" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="15.75" customHeight="1">
       <c r="A45" s="10" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B45" s="9"/>
-      <c r="C45" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="C45" s="4"/>
       <c r="D45" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A46" s="10" t="s">
-        <v>68</v>
+      <c r="A46" s="9" t="s">
+        <v>65</v>
       </c>
       <c r="B46" s="9"/>
-      <c r="C46" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="C46" s="4"/>
       <c r="D46" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A47" s="9" t="s">
-        <v>69</v>
+      <c r="A47" s="10" t="s">
+        <v>66</v>
       </c>
       <c r="B47" s="9"/>
-      <c r="C47" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="C47" s="4"/>
       <c r="D47" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="15.75" customHeight="1">
       <c r="A48" s="10" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B48" s="9"/>
-      <c r="C48" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="C48" s="4"/>
       <c r="D48" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="15.75" customHeight="1">
       <c r="A49" s="10" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B49" s="9"/>
-      <c r="C49" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="C49" s="4"/>
       <c r="D49" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="15.75" customHeight="1">
       <c r="A50" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B50" s="9"/>
-      <c r="C50" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="C50" s="4"/>
       <c r="D50" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="15.75" customHeight="1">
       <c r="A51" s="10" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B51" s="9"/>
-      <c r="C51" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="C51" s="4"/>
       <c r="D51" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="15.75" customHeight="1">
       <c r="A52" s="10" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B52" s="9"/>
-      <c r="C52" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="C52" s="4"/>
       <c r="D52" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="15.75" customHeight="1">
       <c r="A53" s="10" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B53" s="9"/>
-      <c r="C53" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="C53" s="4"/>
       <c r="D53" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="15.75" customHeight="1">
       <c r="A54" s="10" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B54" s="9"/>
-      <c r="C54" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="C54" s="4"/>
       <c r="D54" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="15.75" customHeight="1">
       <c r="A55" s="10" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B55" s="9"/>
-      <c r="C55" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="C55" s="4"/>
       <c r="D55" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A56" s="10" t="s">
-        <v>78</v>
+      <c r="A56" s="9" t="s">
+        <v>75</v>
       </c>
       <c r="B56" s="9"/>
-      <c r="C56" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="C56" s="4"/>
       <c r="D56" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A57" s="9" t="s">
-        <v>79</v>
+      <c r="A57" s="10" t="s">
+        <v>76</v>
       </c>
       <c r="B57" s="9"/>
-      <c r="C57" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="C57" s="4"/>
       <c r="D57" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="15.75" customHeight="1">
       <c r="A58" s="10" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B58" s="9"/>
-      <c r="C58" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="C58" s="4"/>
       <c r="D58" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="15.75" customHeight="1">
       <c r="A59" s="10" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B59" s="9"/>
-      <c r="C59" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="C59" s="4"/>
       <c r="D59" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="15.75" customHeight="1">
       <c r="A60" s="10" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B60" s="9"/>
-      <c r="C60" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="C60" s="4"/>
       <c r="D60" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A61" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="B61" s="9"/>
+      <c r="A61" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>95</v>
+      </c>
       <c r="C61" s="4" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>4</v>
@@ -1585,32 +1530,19 @@
     </row>
     <row r="62" spans="1:4" ht="15.75" customHeight="1">
       <c r="A62" s="6" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>5</v>
+        <v>107</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A63" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
+    <row r="63" spans="1:4" ht="15.75" customHeight="1"/>
     <row r="64" spans="1:4" ht="15.75" customHeight="1"/>
     <row r="65" ht="15.75" customHeight="1"/>
     <row r="66" ht="15.75" customHeight="1"/>
@@ -2529,7 +2461,6 @@
     <row r="979" ht="15.75" customHeight="1"/>
     <row r="980" ht="15.75" customHeight="1"/>
     <row r="981" ht="15.75" customHeight="1"/>
-    <row r="982" ht="15.75" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
